--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/metropolitana.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M358"/>
+  <dimension ref="A1:M364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>24170.57</v>
+        <v>23951.05</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>26260.66</v>
+        <v>26022.16</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>6973.11</v>
+        <v>6909.78</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>25190.81</v>
+        <v>25049.12</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>174867.91</v>
+        <v>173060.31</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>18929.04</v>
+        <v>18733.38</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>41084.21</v>
+        <v>40659.53</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>20973.67</v>
+        <v>20749.22</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>15963.3</v>
+        <v>15792.47</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>9376.27</v>
+        <v>9275.93</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>33256.29</v>
+        <v>32900.4</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>26179.5</v>
+        <v>26033.73</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>50705.76</v>
+        <v>50423.41</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>11916.27</v>
+        <v>11849.91</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>173495.42</v>
+        <v>171588.93</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>20487.16</v>
+        <v>20378.11</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>18314.71</v>
+        <v>18217.23</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>10823.29</v>
+        <v>10765.68</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>23637.67</v>
+        <v>23611.23</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7624.06</v>
+        <v>7615.53</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>23913.44</v>
+        <v>24002.49</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>60187.09</v>
+        <v>60411.22</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>18805.92</v>
+        <v>19013.4</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>34566.91</v>
+        <v>34948.27</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>20363.13</v>
+        <v>20433.26</v>
       </c>
     </row>
     <row r="27">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>16144.78</v>
+        <v>16200.38</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>41681.09</v>
+        <v>41824.64</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>49700.53</v>
+        <v>49871.7</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>47796.59</v>
+        <v>48629.14</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>14340.97</v>
+        <v>14590.77</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>40203.1</v>
+        <v>40903.38</v>
       </c>
     </row>
     <row r="33">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>153592.25</v>
+        <v>154680.16</v>
       </c>
     </row>
     <row r="34">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>26395.4</v>
+        <v>26582.36</v>
       </c>
     </row>
     <row r="35">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>32041.65</v>
+        <v>32268.6</v>
       </c>
     </row>
     <row r="36">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>743345.55</v>
+        <v>748610.75</v>
       </c>
     </row>
     <row r="37">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>323226.04</v>
+        <v>324781.52</v>
       </c>
     </row>
     <row r="38">
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>20384.68</v>
+        <v>20482.78</v>
       </c>
     </row>
     <row r="39">
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>9898.27</v>
+        <v>9945.91</v>
       </c>
     </row>
     <row r="40">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>20496.15</v>
+        <v>20647.1</v>
       </c>
     </row>
     <row r="41">
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>19934.43</v>
+        <v>20081.25</v>
       </c>
     </row>
     <row r="42">
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>34490.66</v>
+        <v>34744.68</v>
       </c>
     </row>
     <row r="43">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>6913.46</v>
+        <v>6964.38</v>
       </c>
     </row>
     <row r="44">
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>19472.32</v>
+        <v>19440.78</v>
       </c>
     </row>
     <row r="45">
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>20757.09</v>
+        <v>20674.73</v>
       </c>
     </row>
     <row r="46">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>53509.24</v>
+        <v>53296.93</v>
       </c>
     </row>
     <row r="47">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>340882.62</v>
+        <v>339530.09</v>
       </c>
     </row>
     <row r="48">
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>52612.87</v>
+        <v>52404.12</v>
       </c>
     </row>
     <row r="49">
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>13013.43</v>
+        <v>12995.26</v>
       </c>
     </row>
     <row r="50">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>20757.09</v>
+        <v>20728.12</v>
       </c>
     </row>
     <row r="51">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>67799.44</v>
+        <v>67704.81</v>
       </c>
     </row>
     <row r="52">
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>20257.65</v>
+        <v>20365.42</v>
       </c>
     </row>
     <row r="53">
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>15364.48</v>
+        <v>15446.22</v>
       </c>
     </row>
     <row r="54">
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>54900.39</v>
+        <v>55192.44</v>
       </c>
     </row>
     <row r="55">
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>14903.55</v>
+        <v>15011.05</v>
       </c>
     </row>
     <row r="56">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>7682.24</v>
+        <v>7737.66</v>
       </c>
     </row>
     <row r="57">
@@ -3932,7 +3932,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>34256.39</v>
+        <v>34503.48</v>
       </c>
     </row>
     <row r="58">
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>14852.33</v>
+        <v>14959.47</v>
       </c>
     </row>
     <row r="59">
@@ -4054,7 +4054,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>33605.05</v>
+        <v>33144.53</v>
       </c>
     </row>
     <row r="60">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>6859.59</v>
+        <v>6765.58</v>
       </c>
     </row>
     <row r="61">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>20625.1</v>
+        <v>20342.45</v>
       </c>
     </row>
     <row r="62">
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>31132.44</v>
+        <v>30705.8</v>
       </c>
     </row>
     <row r="63">
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>21546.64</v>
+        <v>21251.37</v>
       </c>
     </row>
     <row r="64">
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>28476.82</v>
+        <v>28086.57</v>
       </c>
     </row>
     <row r="65">
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>8497.83</v>
+        <v>8383.280000000001</v>
       </c>
     </row>
     <row r="66">
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>28582.91</v>
+        <v>28197.6</v>
       </c>
     </row>
     <row r="67">
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>10149.07</v>
+        <v>10012.25</v>
       </c>
     </row>
     <row r="68">
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>66276.87</v>
+        <v>65383.41</v>
       </c>
     </row>
     <row r="69">
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>10100.57</v>
+        <v>9992.190000000001</v>
       </c>
     </row>
     <row r="70">
@@ -4729,7 +4729,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>180843.68</v>
+        <v>178903.18</v>
       </c>
     </row>
     <row r="71">
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>20137.05</v>
+        <v>20049.02</v>
       </c>
     </row>
     <row r="72">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>21213.34</v>
+        <v>21120.6</v>
       </c>
     </row>
     <row r="73">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>21213.34</v>
+        <v>21120.6</v>
       </c>
     </row>
     <row r="74">
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>42339.42</v>
+        <v>42154.33</v>
       </c>
     </row>
     <row r="75">
@@ -5034,7 +5034,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>7088.24</v>
+        <v>7057.25</v>
       </c>
     </row>
     <row r="76">
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>68388.00999999999</v>
+        <v>68186.2</v>
       </c>
     </row>
     <row r="77">
@@ -5156,7 +5156,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>14095.93</v>
+        <v>14025.77</v>
       </c>
     </row>
     <row r="78">
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>49084.16</v>
+        <v>48839.84</v>
       </c>
     </row>
     <row r="79">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>27265.56</v>
+        <v>26931.36</v>
       </c>
     </row>
     <row r="80">
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>7111.19</v>
+        <v>7046.76</v>
       </c>
     </row>
     <row r="81">
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>8700.07</v>
+        <v>8621.24</v>
       </c>
     </row>
     <row r="82">
@@ -5461,7 +5461,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>20620.34</v>
+        <v>20433.49</v>
       </c>
     </row>
     <row r="83">
@@ -5522,7 +5522,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>33951.49</v>
+        <v>33643.85</v>
       </c>
     </row>
     <row r="84">
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>19458.03</v>
+        <v>19432.68</v>
       </c>
     </row>
     <row r="85">
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>54398.18</v>
+        <v>54327.33</v>
       </c>
     </row>
     <row r="86">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>10874.01</v>
+        <v>10859.84</v>
       </c>
     </row>
     <row r="87">
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>7645.16</v>
+        <v>7635.21</v>
       </c>
     </row>
     <row r="88">
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>83796.08</v>
+        <v>83686.95</v>
       </c>
     </row>
     <row r="89">
@@ -5892,7 +5892,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>12816.69</v>
+        <v>12800</v>
       </c>
     </row>
     <row r="90">
@@ -5953,13 +5953,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>7791.56</v>
+        <v>7781.42</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>14-666-CM25</t>
+          <t>14-665-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>8698.77</v>
+        <v>7822.25</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2580-1265-CM25</t>
+          <t>14-666-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6075,13 +6075,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>170450.36</v>
+        <v>8730.33</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>14-665-CM25</t>
+          <t>2580-1265-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6106,12 +6106,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>7793.97</v>
+        <v>171068.81</v>
       </c>
     </row>
     <row r="94">
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>53386.99</v>
+        <v>53622.89</v>
       </c>
     </row>
     <row r="95">
@@ -6258,7 +6258,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>22026.03</v>
+        <v>22123.36</v>
       </c>
     </row>
     <row r="96">
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>26831.02</v>
+        <v>26949.57</v>
       </c>
     </row>
     <row r="97">
@@ -6380,7 +6380,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>16551.35</v>
+        <v>16624.49</v>
       </c>
     </row>
     <row r="98">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>7240.68</v>
+        <v>7259.76</v>
       </c>
     </row>
     <row r="99">
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>500066.59</v>
+        <v>501384.71</v>
       </c>
     </row>
     <row r="100">
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>508081.52</v>
+        <v>507409.75</v>
       </c>
     </row>
     <row r="101">
@@ -6624,7 +6624,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>10928.78</v>
+        <v>10914.33</v>
       </c>
     </row>
     <row r="102">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>35856.94</v>
+        <v>35909.28</v>
       </c>
     </row>
     <row r="103">
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>48805.27</v>
+        <v>48876.52</v>
       </c>
     </row>
     <row r="104">
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>625125.4</v>
+        <v>626037.92</v>
       </c>
     </row>
     <row r="105">
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>12601.89</v>
+        <v>12694.57</v>
       </c>
     </row>
     <row r="106">
@@ -6929,7 +6929,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>33024.76</v>
+        <v>33267.61</v>
       </c>
     </row>
     <row r="107">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>24365.83</v>
+        <v>24545.01</v>
       </c>
     </row>
     <row r="108">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>71542.82000000001</v>
+        <v>72194.91</v>
       </c>
     </row>
     <row r="109">
@@ -7112,7 +7112,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>64854.28</v>
+        <v>65445.42</v>
       </c>
     </row>
     <row r="110">
@@ -7173,7 +7173,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>149080.41</v>
+        <v>150779.08</v>
       </c>
     </row>
     <row r="111">
@@ -7234,7 +7234,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>36650.57</v>
+        <v>37068.18</v>
       </c>
     </row>
     <row r="112">
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>7367.91</v>
+        <v>7464.83</v>
       </c>
     </row>
     <row r="113">
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>28997.35</v>
+        <v>29378.8</v>
       </c>
     </row>
     <row r="114">
@@ -7421,13 +7421,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>45223.96</v>
+        <v>45818.88</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>14-687-CM25</t>
+          <t>1111089-743-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7447,17 +7447,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>QUALITY FOR TECHNOLOGY LIMITADA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
+          <t>76.590.008-5</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7482,13 +7482,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>19898.69</v>
+        <v>64624.59</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1111089-743-CM25</t>
+          <t>1111089-726-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>QUALITY FOR TECHNOLOGY LIMITADA</t>
+          <t>KUANTUM SPA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.590.008-5</t>
+          <t>76.553.335-K</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>63785.5</v>
+        <v>32131.97</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1111089-726-CM25</t>
+          <t>14-687-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7569,17 +7569,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>KUANTUM SPA</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>76.553.335-K</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7604,7 +7604,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>31714.77</v>
+        <v>20160.45</v>
       </c>
     </row>
     <row r="118">
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>87093.81</v>
+        <v>88313.88</v>
       </c>
     </row>
     <row r="119">
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>18816.06</v>
+        <v>19079.65</v>
       </c>
     </row>
     <row r="120">
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>8740.049999999999</v>
+        <v>8862.49</v>
       </c>
     </row>
     <row r="121">
@@ -7848,7 +7848,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>68963.97</v>
+        <v>69427.17999999999</v>
       </c>
     </row>
     <row r="122">
@@ -7913,7 +7913,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>130529.49</v>
+        <v>131406.22</v>
       </c>
     </row>
     <row r="123">
@@ -7974,13 +7974,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>63513.55</v>
+        <v>63940.15</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1590-566-CM25</t>
+          <t>1385462-207-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.301.000-9</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8020,12 +8020,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>ZERVIZ</t>
+          <t>LIVISTER CHILE SPA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.755.489-3</t>
+          <t>77.622.841-9</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8035,13 +8035,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>65403.83</v>
+        <v>400983.3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>654478-776-CM25</t>
+          <t>1590-566-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.980.140-7</t>
+          <t>61.301.000-9</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE PREVENCION DEL DELITO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>ZERVIZ</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>76.755.489-3</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8096,13 +8096,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>263798</v>
+        <v>65849.49000000001</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>591-7730-SE25</t>
+          <t>654478-776-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8122,17 +8122,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.980.140-7</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SUBSECRETARIA DE PREVENCION DEL DELITO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8142,32 +8142,28 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>92.580.000-7</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>895721.87</v>
+        <v>265595.52</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1751-131-CM25</t>
+          <t>591-7730-SE25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8187,17 +8183,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.975.600-2</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>FISCALIZACION Y CONTROL</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8207,28 +8203,32 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr"/>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>228652.92</v>
+        <v>901825.33</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>812261-7589-CM25</t>
+          <t>1314-54-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8248,17 +8248,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8268,12 +8268,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8283,13 +8283,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>77949.86</v>
+        <v>28504.3</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1385462-207-CM25</t>
+          <t>609-569-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8329,12 +8329,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>LIVISTER CHILE SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>77.622.841-9</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8344,13 +8344,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>398269.49</v>
+        <v>68833.08</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1314-54-CM25</t>
+          <t>812261-7589-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8370,17 +8370,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>77.714.387-5</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8405,13 +8405,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>28311.39</v>
+        <v>78481.00999999999</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>609-569-CM25</t>
+          <t>1751-131-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.975.600-2</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>FISCALIZACION Y CONTROL</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8451,12 +8451,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8466,7 +8466,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>68367.22</v>
+        <v>230210.97</v>
       </c>
     </row>
     <row r="132">
@@ -8527,7 +8527,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>57567.36</v>
+        <v>56458.54</v>
       </c>
     </row>
     <row r="133">
@@ -8588,13 +8588,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>29849.98</v>
+        <v>29161.74</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2793-1481-CM25</t>
+          <t>812261-7572-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8614,17 +8614,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8634,12 +8634,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8649,7 +8649,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>24640.53</v>
+        <v>48887.01</v>
       </c>
     </row>
     <row r="135">
@@ -8710,13 +8710,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>74735.08</v>
+        <v>73826.19</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>812261-7572-CM25</t>
+          <t>812261-7571-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8771,13 +8771,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>49488.86</v>
+        <v>291592.37</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>812261-7571-CM25</t>
+          <t>2793-1481-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8797,17 +8797,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>Iluste Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>295182.2</v>
+        <v>24340.87</v>
       </c>
     </row>
     <row r="138">
@@ -8893,7 +8893,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>27670.74</v>
+        <v>27289.32</v>
       </c>
     </row>
     <row r="139">
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>22993.68</v>
+        <v>22957.04</v>
       </c>
     </row>
     <row r="140">
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>59467.99</v>
+        <v>59373.22</v>
       </c>
     </row>
     <row r="141">
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>36371.82</v>
+        <v>36431.33</v>
       </c>
     </row>
     <row r="142">
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>20903.34</v>
+        <v>20937.55</v>
       </c>
     </row>
     <row r="143">
@@ -9198,7 +9198,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>20416.71</v>
+        <v>20406.49</v>
       </c>
     </row>
     <row r="144">
@@ -9259,7 +9259,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>21689.45</v>
+        <v>21678.6</v>
       </c>
     </row>
     <row r="145">
@@ -9320,7 +9320,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>7913.17</v>
+        <v>7909.21</v>
       </c>
     </row>
     <row r="146">
@@ -9381,7 +9381,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>17783.4</v>
+        <v>17774.5</v>
       </c>
     </row>
     <row r="147">
@@ -9442,7 +9442,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>49521.64</v>
+        <v>49351.13</v>
       </c>
     </row>
     <row r="148">
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>52482.23</v>
+        <v>52201.04</v>
       </c>
     </row>
     <row r="149">
@@ -9564,7 +9564,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>580026</v>
+        <v>576310.49</v>
       </c>
     </row>
     <row r="150">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>25585.69</v>
+        <v>25748.1</v>
       </c>
     </row>
     <row r="151">
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>8361.34</v>
+        <v>8414.41</v>
       </c>
     </row>
     <row r="152">
@@ -9751,7 +9751,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1798.14</v>
+        <v>1821.86</v>
       </c>
     </row>
     <row r="153">
@@ -9812,7 +9812,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>654773.7</v>
+        <v>664434.1899999999</v>
       </c>
     </row>
     <row r="154">
@@ -9873,7 +9873,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>51350.45</v>
+        <v>52571.41</v>
       </c>
     </row>
     <row r="155">
@@ -9934,7 +9934,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>11315.89</v>
+        <v>11584.95</v>
       </c>
     </row>
     <row r="156">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>22959.37</v>
+        <v>23640.04</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>584264-27-CM26</t>
+          <t>5768-23-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10021,17 +10021,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>69.255.500-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10041,12 +10041,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>XIMENA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>76.667.903-k</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10056,13 +10056,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>31260.61</v>
+        <v>30980.89</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5768-23-CM26</t>
+          <t>584264-27-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10082,17 +10082,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.255.500-7</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10102,12 +10102,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>XIMENA</t>
+          <t>SOLNET SPA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>76.667.903-k</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10117,13 +10117,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>30108.34</v>
+        <v>32166.56</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>761-31-CM26</t>
+          <t>730566-20-SE26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10163,28 +10163,32 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>FERNANDO MARCELO</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr"/>
+          <t>76.811.563-K</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>26957.34</v>
+        <v>556180.29</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>730566-20-SE26</t>
+          <t>761-31-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10209,12 +10213,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10224,26 +10228,22 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>FERNANDO MARCELO</t>
+          <t>ANDES DIGITAL</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>76.811.563-K</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.975.787-2</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>558501.78</v>
+        <v>26845.29</v>
       </c>
     </row>
     <row r="161">
@@ -10304,7 +10304,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>78226.38</v>
+        <v>77589.44</v>
       </c>
     </row>
     <row r="162">
@@ -10369,7 +10369,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>425249.38</v>
+        <v>421786.91</v>
       </c>
     </row>
     <row r="163">
@@ -10434,7 +10434,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>7443.37</v>
+        <v>7459.5</v>
       </c>
     </row>
     <row r="164">
@@ -10495,7 +10495,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>253458.04</v>
+        <v>254565.52</v>
       </c>
     </row>
     <row r="165">
@@ -10556,7 +10556,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>18428.71</v>
+        <v>18509.23</v>
       </c>
     </row>
     <row r="166">
@@ -10617,7 +10617,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>25339.34</v>
+        <v>25450.06</v>
       </c>
     </row>
     <row r="167">
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>19954.43</v>
+        <v>20041.62</v>
       </c>
     </row>
     <row r="168">
@@ -10739,7 +10739,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>10842.94</v>
+        <v>10787.97</v>
       </c>
     </row>
     <row r="169">
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>46636.29</v>
+        <v>46399.86</v>
       </c>
     </row>
     <row r="170">
@@ -10861,13 +10861,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>8493.15</v>
+        <v>8545.73</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>45-12-CM26</t>
+          <t>711841-49-SE26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10907,28 +10907,32 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>74363.67999999999</v>
+        <v>224012.71</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>711841-49-SE26</t>
+          <t>45-12-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10953,12 +10957,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10968,26 +10972,22 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>ANDES DIGITAL</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.975.787-2</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>222685.76</v>
+        <v>74806.8</v>
       </c>
     </row>
     <row r="173">
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>32184.57</v>
+        <v>32127.7</v>
       </c>
     </row>
     <row r="174">
@@ -11109,7 +11109,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>7542.22</v>
+        <v>7535.11</v>
       </c>
     </row>
     <row r="175">
@@ -11170,7 +11170,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>112086.39</v>
+        <v>111309.26</v>
       </c>
     </row>
     <row r="176">
@@ -11231,7 +11231,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>72341.53999999999</v>
+        <v>71839.97</v>
       </c>
     </row>
     <row r="177">
@@ -11292,13 +11292,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>17554</v>
+        <v>17432.29</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2341-88-CM26</t>
+          <t>619-53-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11318,17 +11318,17 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>69.072.700-5</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11338,12 +11338,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11353,13 +11353,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>15657.11</v>
+        <v>72334.02</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>619-53-CM26</t>
+          <t>2341-88-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11379,17 +11379,17 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11399,12 +11399,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11414,7 +11414,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>72413.42999999999</v>
+        <v>15639.94</v>
       </c>
     </row>
     <row r="180">
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>27839.4</v>
+        <v>27702.12</v>
       </c>
     </row>
     <row r="181">
@@ -11540,7 +11540,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>7941.53</v>
+        <v>7902.37</v>
       </c>
     </row>
     <row r="182">
@@ -11601,13 +11601,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>43664.84</v>
+        <v>43455.72</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>711-697-CM25</t>
+          <t>5153-349-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11627,17 +11627,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.212.000-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11647,12 +11647,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Ingenieria de Software Ltda.</t>
+          <t>Pragma Informatica S.A.</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>85.928.600-3</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11662,13 +11662,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>59818.67</v>
+        <v>77108.33</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1602-19-CM26</t>
+          <t>5153-348-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11688,17 +11688,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>SOLUCIONES TECNOLÓGICAS COORDENADA SPA</t>
+          <t>Pragma Informatica S.A.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>76.489.853-2</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11723,13 +11723,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>56814.7</v>
+        <v>75841.3</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>5153-348-CM26</t>
+          <t>711-697-CM25</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11749,17 +11749,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.212.000-5</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11769,12 +11769,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>Ingenieria de Software Ltda.</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>85.928.600-3</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -11784,13 +11784,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>76218.81</v>
+        <v>59522.39</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5153-349-CM26</t>
+          <t>1602-19-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11810,17 +11810,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11830,12 +11830,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>SOLUCIONES TECNOLÓGICAS COORDENADA SPA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>76.489.853-2</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -11845,7 +11845,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>77492.14</v>
+        <v>56533.3</v>
       </c>
     </row>
     <row r="187">
@@ -11906,7 +11906,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>26398.81</v>
+        <v>26266.96</v>
       </c>
     </row>
     <row r="188">
@@ -11967,7 +11967,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>11622.2</v>
+        <v>11564.16</v>
       </c>
     </row>
     <row r="189">
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>16369.88</v>
+        <v>16288.11</v>
       </c>
     </row>
     <row r="190">
@@ -12089,7 +12089,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>37857.1</v>
+        <v>37668.01</v>
       </c>
     </row>
     <row r="191">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>19714.43</v>
+        <v>19615.96</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1029940-15-CM26</t>
+          <t>4754-3-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>62.000.370-0</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL PATRIMONIO CULTURAL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>76.198.095-5</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12211,13 +12211,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>13819.46</v>
+        <v>65982.95</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>4754-3-CM26</t>
+          <t>1029940-15-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12242,12 +12242,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>62.000.370-0</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SUBSECRETARIA DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
+          <t>ZECOVERY LTDA   -    EXEC</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>76.198.095-5</t>
+          <t>76.260.080-3</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12272,7 +12272,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>66157.17</v>
+        <v>13783.07</v>
       </c>
     </row>
     <row r="194">
@@ -12333,7 +12333,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>25881.76</v>
+        <v>26051.5</v>
       </c>
     </row>
     <row r="195">
@@ -12394,13 +12394,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>20100.15</v>
+        <v>20231.97</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>587-61-CM26</t>
+          <t>2216-95-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12420,17 +12420,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12440,12 +12440,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Asimov Consultores SpA</t>
+          <t>SERVICIOS INFORMÁTICOS COMMUNITY MARKETPLACE LIMITADA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>76.802.163-5</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -12455,13 +12455,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>80553.58</v>
+        <v>431038</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2216-95-CM26</t>
+          <t>587-61-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12481,17 +12481,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>SERVICIOS INFORMÁTICOS COMMUNITY MARKETPLACE LIMITADA</t>
+          <t>Asimov Consultores SpA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>76.802.163-5</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -12516,7 +12516,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>429970.89</v>
+        <v>80753.5</v>
       </c>
     </row>
     <row r="198">
@@ -12577,7 +12577,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>26642.7</v>
+        <v>27397.66</v>
       </c>
     </row>
     <row r="199">
@@ -12638,7 +12638,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>7531.87</v>
+        <v>7557.43</v>
       </c>
     </row>
     <row r="200">
@@ -12699,7 +12699,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>28102.38</v>
+        <v>28553.99</v>
       </c>
     </row>
     <row r="201">
@@ -12760,13 +12760,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>23248.49</v>
+        <v>23299.58</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1460278-83-CM26</t>
+          <t>2686-60-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12791,12 +12791,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>69.071.500-7</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>I MUNICIPALIDAD DE COLINA</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12806,12 +12806,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>ALTAVOZ SOCIEDAD ANONIMA</t>
+          <t>UBIQUITY SPA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>96.827.350-7</t>
+          <t>76.423.027-2</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -12821,13 +12821,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>20637.02</v>
+        <v>7834.57</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1460278-82-CM26</t>
+          <t>1588-29-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12847,17 +12847,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>72.443.600-5</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12867,12 +12867,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>ALTAVOZ SOCIEDAD ANONIMA</t>
+          <t>Smartnodus SpA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>96.827.350-7</t>
+          <t>76.461.797-5</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -12882,7 +12882,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>26257.49</v>
+        <v>25308.59</v>
       </c>
     </row>
     <row r="204">
@@ -12943,13 +12943,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>218707.38</v>
+        <v>215927.46</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1588-29-CM26</t>
+          <t>1460278-82-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12969,17 +12969,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>72.443.600-5</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12989,12 +12989,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Smartnodus SpA</t>
+          <t>ALTAVOZ SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>76.461.797-5</t>
+          <t>96.827.350-7</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -13004,13 +13004,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>25634.42</v>
+        <v>25923.74</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2686-60-CM26</t>
+          <t>1460278-83-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>69.071.500-7</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLINA</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13050,12 +13050,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>UBIQUITY SPA</t>
+          <t>ALTAVOZ SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>76.423.027-2</t>
+          <t>96.827.350-7</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -13065,13 +13065,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>7935.43</v>
+        <v>20374.71</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>45-46-CM26</t>
+          <t>4956-49-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13091,17 +13091,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>69.071.200-8</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>I MUNICIPALIDAD DE RENCA</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENVISION INVERSIONES LIMITADA </t>
+          <t>MEETCARD</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>76.693.295-9</t>
+          <t>76.437.288-3</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -13126,7 +13126,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>35524.85</v>
+        <v>65999.97</v>
       </c>
     </row>
     <row r="208">
@@ -13187,13 +13187,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>57495.4</v>
+        <v>57099.1</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>4956-49-CM26</t>
+          <t>45-46-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13213,17 +13213,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>69.071.200-8</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENCA</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13233,12 +13233,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>MEETCARD</t>
+          <t xml:space="preserve">ENVISION INVERSIONES LIMITADA </t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>76.437.288-3</t>
+          <t>76.693.295-9</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13248,7 +13248,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>66458.03999999999</v>
+        <v>35279.98</v>
       </c>
     </row>
     <row r="210">
@@ -13309,7 +13309,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>32345.68</v>
+        <v>32857.8</v>
       </c>
     </row>
     <row r="211">
@@ -13370,7 +13370,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>30621.24</v>
+        <v>31106.05</v>
       </c>
     </row>
     <row r="212">
@@ -13431,7 +13431,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>55715.33</v>
+        <v>55721.69</v>
       </c>
     </row>
     <row r="213">
@@ -13492,7 +13492,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>72784.25</v>
+        <v>72859.02</v>
       </c>
     </row>
     <row r="214">
@@ -13553,13 +13553,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>10993.16</v>
+        <v>11004.45</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>5768-43-CM26</t>
+          <t>4754-5-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13599,12 +13599,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Inteldata Ltda.</t>
+          <t>MCL CONSULTING</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>76.414.840-1</t>
+          <t>76.314.701-0</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -13614,13 +13614,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>18729.09</v>
+        <v>15382.69</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>4754-5-CM26</t>
+          <t>5768-43-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13645,12 +13645,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13660,12 +13660,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>MCL CONSULTING</t>
+          <t>Inteldata Ltda.</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>76.314.701-0</t>
+          <t>76.414.840-1</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -13675,7 +13675,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>15316.87</v>
+        <v>18809.57</v>
       </c>
     </row>
     <row r="217">
@@ -13736,7 +13736,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>58840.32</v>
+        <v>58687.73</v>
       </c>
     </row>
     <row r="218">
@@ -13797,13 +13797,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>1722655.54</v>
+        <v>1703050.45</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>5520-1119-CM26</t>
+          <t>2434-30-SE26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13828,12 +13828,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13843,28 +13843,32 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>ZECOVERY LTDA   -    EXEC</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>50434.56</v>
+        <v>4766.29</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2434-30-SE26</t>
+          <t>5520-1119-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13889,12 +13893,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13904,26 +13908,22 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>4793.03</v>
+        <v>50153.16</v>
       </c>
     </row>
     <row r="221">
@@ -13984,7 +13984,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>19907.64</v>
+        <v>19825.16</v>
       </c>
     </row>
     <row r="222">
@@ -14045,7 +14045,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>45615.72</v>
+        <v>44561.65</v>
       </c>
     </row>
     <row r="223">
@@ -14106,7 +14106,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>33148.03</v>
+        <v>32382.06</v>
       </c>
     </row>
     <row r="224">
@@ -14167,7 +14167,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>85013.49000000001</v>
+        <v>82092.52</v>
       </c>
     </row>
     <row r="225">
@@ -14228,13 +14228,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>42973.85</v>
+        <v>42018.78</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>5148-54-CM26</t>
+          <t>2792-98-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>Iluste Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14274,12 +14274,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>SPIELUP SPA</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>76.582.047-2</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -14289,13 +14289,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>41132.12</v>
+        <v>46257.04</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2792-98-CM26</t>
+          <t>5148-54-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14320,12 +14320,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14335,12 +14335,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>SPIELUP SPA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>76.582.047-2</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -14350,7 +14350,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>47232</v>
+        <v>40283.06</v>
       </c>
     </row>
     <row r="228">
@@ -14411,7 +14411,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>10747.29</v>
+        <v>10432.81</v>
       </c>
     </row>
     <row r="229">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>21835.91</v>
+        <v>21843.55</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>165-24-CM26</t>
+          <t>1191449-33-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14503,12 +14503,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>60.905.006-3</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>ARCHIVO NACIONAL</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14518,12 +14518,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>BRAINSOFT</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>76.261.280-1</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>18875.61</v>
+        <v>16460.51</v>
       </c>
     </row>
     <row r="231">
@@ -14594,13 +14594,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>20768.36</v>
+        <v>20918.87</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1191449-33-CM26</t>
+          <t>165-24-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>60.905.006-3</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>ARCHIVO NACIONAL</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>BRAINSOFT</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>76.261.280-1</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -14655,7 +14655,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>16342.08</v>
+        <v>19012.41</v>
       </c>
     </row>
     <row r="233">
@@ -14716,7 +14716,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>246401.07</v>
+        <v>245768.22</v>
       </c>
     </row>
     <row r="234">
@@ -14777,7 +14777,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>39349.31</v>
+        <v>39248.25</v>
       </c>
     </row>
     <row r="235">
@@ -14838,7 +14838,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>71127.05</v>
+        <v>71961.64</v>
       </c>
     </row>
     <row r="236">
@@ -14899,7 +14899,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>13584.72</v>
+        <v>13762.33</v>
       </c>
     </row>
     <row r="237">
@@ -14960,7 +14960,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>64701.81</v>
+        <v>65552.49000000001</v>
       </c>
     </row>
     <row r="238">
@@ -15021,7 +15021,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>60879.62</v>
+        <v>61680.12</v>
       </c>
     </row>
     <row r="239">
@@ -15082,13 +15082,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>28960.64</v>
+        <v>29282.56</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2581-5-CM26</t>
+          <t>1186229-57-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15113,12 +15113,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>69.070.200-2</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCHALI</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15128,12 +15128,12 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>Pragma Informatica S.A.</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -15143,13 +15143,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>33506.77</v>
+        <v>681911.34</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1186229-57-CM26</t>
+          <t>5403-17-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15174,12 +15174,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>61.978.810-9</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>COMISION NACIONAL DE ACREDITACION</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15189,12 +15189,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>LIVISTER CHILE SPA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>77.622.841-9</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -15204,13 +15204,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>676558.0699999999</v>
+        <v>205272.38</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>5403-17-CM26</t>
+          <t>2581-5-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15235,12 +15235,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.978.810-9</t>
+          <t>69.070.200-2</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE ACREDITACION</t>
+          <t>I MUNICIPALIDAD DE CONCHALI</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15250,12 +15250,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>LIVISTER CHILE SPA</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>77.622.841-9</t>
+          <t>76.376.088-k</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -15265,7 +15265,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>203660.91</v>
+        <v>33771.89</v>
       </c>
     </row>
     <row r="243">
@@ -15326,7 +15326,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>69732.42</v>
+        <v>70162.33</v>
       </c>
     </row>
     <row r="244">
@@ -15387,7 +15387,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>46501.24</v>
+        <v>46506.05</v>
       </c>
     </row>
     <row r="245">
@@ -15448,7 +15448,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>84032.19</v>
+        <v>84040.89</v>
       </c>
     </row>
     <row r="246">
@@ -15513,7 +15513,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>68820.44</v>
+        <v>68827.57000000001</v>
       </c>
     </row>
     <row r="247">
@@ -15574,7 +15574,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>10951.47</v>
+        <v>10835.01</v>
       </c>
     </row>
     <row r="248">
@@ -15635,13 +15635,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>18624.4</v>
+        <v>18426.35</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>5627-111-CM26</t>
+          <t>1191449-55-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15666,12 +15666,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.905.006-3</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>ARCHIVO NACIONAL</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15681,12 +15681,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>76.185.219-1</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -15696,7 +15696,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>10585.99</v>
+        <v>28748.7</v>
       </c>
     </row>
     <row r="250">
@@ -15757,13 +15757,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>8945.25</v>
+        <v>8785.35</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1191449-55-CM26</t>
+          <t>5627-111-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15788,12 +15788,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>60.905.006-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>ARCHIVO NACIONAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -15803,12 +15803,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
+          <t>VICTORIA SPA</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>76.185.219-1</t>
+          <t>76.188.587-1</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -15818,7 +15818,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>29271.95</v>
+        <v>10396.76</v>
       </c>
     </row>
     <row r="252">
@@ -15879,7 +15879,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>31362.8</v>
+        <v>30970.65</v>
       </c>
     </row>
     <row r="253">
@@ -15940,7 +15940,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>497645.55</v>
+        <v>498484.99</v>
       </c>
     </row>
     <row r="254">
@@ -16005,7 +16005,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>7262.67</v>
+        <v>7274.93</v>
       </c>
     </row>
     <row r="255">
@@ -16066,7 +16066,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>32520.19</v>
+        <v>32773.79</v>
       </c>
     </row>
     <row r="256">
@@ -16127,7 +16127,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>13880.57</v>
+        <v>13988.81</v>
       </c>
     </row>
     <row r="257">
@@ -16188,7 +16188,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>23288.76</v>
+        <v>23470.38</v>
       </c>
     </row>
     <row r="258">
@@ -16249,7 +16249,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>53523.59</v>
+        <v>53958.89</v>
       </c>
     </row>
     <row r="259">
@@ -16310,7 +16310,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>36564.84</v>
+        <v>36761.26</v>
       </c>
     </row>
     <row r="260">
@@ -16371,13 +16371,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>7335.41</v>
+        <v>7350.17</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1005498-52-CM26</t>
+          <t>1480134-17-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16397,17 +16397,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>60.810.000-8</t>
+          <t>69.255.600-3</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+          <t>MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16417,12 +16417,12 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>SOLUCIONES TECNOLÓGICAS COORDENADA SPA</t>
+          <t>ANIDA CONSULTORES S A</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>76.489.853-2</t>
+          <t>77.680.090-2</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
@@ -16432,13 +16432,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>105900.59</v>
+        <v>7312.15</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>756-66-CM26</t>
+          <t>1177296-173-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16458,17 +16458,17 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>60.701.000-5</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16478,12 +16478,12 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>INFO-UPDATE LIMITADA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>76.023.530-k</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
@@ -16493,13 +16493,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>34101.14</v>
+        <v>61316.16</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>759-104-CM26</t>
+          <t>1005498-52-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>61.001.000-8</t>
+          <t>60.810.000-8</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>PAULA ALEJANDRA QUITRAL HERRERA, SERVICIOS INFORMATICOS, EMPRESA INDIV</t>
+          <t>SOLUCIONES TECNOLÓGICAS COORDENADA SPA</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>76.092.019-3</t>
+          <t>76.489.853-2</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
@@ -16554,13 +16554,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>13242.07</v>
+        <v>105490.17</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1177296-173-CM26</t>
+          <t>756-66-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16580,17 +16580,17 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>60.701.000-5</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMA</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -16600,12 +16600,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>INFO-UPDATE LIMITADA</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.023.530-k</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
@@ -16615,13 +16615,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>61554.72</v>
+        <v>33968.98</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1480134-17-CM26</t>
+          <t>759-104-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16641,17 +16641,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>69.255.600-3</t>
+          <t>61.001.000-8</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16661,12 +16661,12 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>ANIDA CONSULTORES S A</t>
+          <t>PAULA ALEJANDRA QUITRAL HERRERA, SERVICIOS INFORMATICOS, EMPRESA INDIV</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>77.680.090-2</t>
+          <t>76.092.019-3</t>
         </is>
       </c>
       <c r="K265" t="inlineStr"/>
@@ -16676,7 +16676,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>7340.6</v>
+        <v>13190.75</v>
       </c>
     </row>
     <row r="266">
@@ -16737,7 +16737,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>8796.709999999999</v>
+        <v>8857.620000000001</v>
       </c>
     </row>
     <row r="267">
@@ -16798,7 +16798,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>592589.62</v>
+        <v>587107.27</v>
       </c>
     </row>
     <row r="268">
@@ -16859,7 +16859,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>65236.42</v>
+        <v>65024.86</v>
       </c>
     </row>
     <row r="269">
@@ -16924,7 +16924,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>360947.33</v>
+        <v>357020.86</v>
       </c>
     </row>
     <row r="270">
@@ -16989,7 +16989,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1641207.55</v>
+        <v>1643132.54</v>
       </c>
     </row>
     <row r="271">
@@ -17050,13 +17050,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>22662.15</v>
+        <v>22688.73</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1177296-550-CM25</t>
+          <t>5768-77-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17081,12 +17081,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17096,12 +17096,12 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K272" t="inlineStr"/>
@@ -17111,13 +17111,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>313385.18</v>
+        <v>18773.77</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>5768-77-CM26</t>
+          <t>463-27-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17137,17 +17137,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>71.294.800-0</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CENTRO DE INFORMACION DE RECURSOS NATURALES</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17157,12 +17157,12 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>ESRI CHILE S A</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.504.980-6</t>
         </is>
       </c>
       <c r="K273" t="inlineStr"/>
@@ -17172,13 +17172,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>18606.27</v>
+        <v>33105.94</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>463-27-CM26</t>
+          <t>1177296-550-CM25</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17198,17 +17198,17 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>71.294.800-0</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>CENTRO DE INFORMACION DE RECURSOS NATURALES</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17218,12 +17218,12 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>ESRI CHILE S A</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>76.504.980-6</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K274" t="inlineStr"/>
@@ -17233,13 +17233,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>32810.58</v>
+        <v>316206.29</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2268-87-CM26</t>
+          <t>5574-43-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17264,12 +17264,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17279,12 +17279,12 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>TBUSINESS SPA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>77.009.886-6</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K275" t="inlineStr"/>
@@ -17294,13 +17294,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>63400.07</v>
+        <v>57074.88</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>599-82-CM26</t>
+          <t>5627-131-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17320,17 +17320,17 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17340,12 +17340,12 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
+          <t>76.083.021-6</t>
         </is>
       </c>
       <c r="K276" t="inlineStr"/>
@@ -17355,13 +17355,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>70936.44</v>
+        <v>11589.63</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2766-277-CM26</t>
+          <t>2083-1-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17381,17 +17381,17 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>71.294.800-0</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>CENTRO DE INFORMACION DE RECURSOS NATURALES</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17401,12 +17401,12 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>ESRI CHILE S A</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>76.504.980-6</t>
         </is>
       </c>
       <c r="K277" t="inlineStr"/>
@@ -17416,13 +17416,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>13893.3</v>
+        <v>11116.24</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2083-1-CM26</t>
+          <t>2268-87-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17442,17 +17442,17 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>71.294.800-0</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>CENTRO DE INFORMACION DE RECURSOS NATURALES</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17462,12 +17462,12 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>ESRI CHILE S A</t>
+          <t>TBUSINESS SPA</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>76.504.980-6</t>
+          <t>77.009.886-6</t>
         </is>
       </c>
       <c r="K278" t="inlineStr"/>
@@ -17477,13 +17477,13 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>11029.98</v>
+        <v>63895.88</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>5627-131-CM26</t>
+          <t>599-82-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17503,17 +17503,17 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17523,12 +17523,12 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>76.083.021-6</t>
+          <t>77.430.680-3</t>
         </is>
       </c>
       <c r="K279" t="inlineStr"/>
@@ -17538,13 +17538,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>11499.69</v>
+        <v>71491.19</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>5574-43-CM26</t>
+          <t>2766-277-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17569,12 +17569,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17599,13 +17599,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>56632</v>
+        <v>14001.95</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1305552-66-CM26</t>
+          <t>599-58-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -17625,17 +17625,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>61.981.030-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -17645,12 +17645,12 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>ANDESTIC SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>76.031.392-0</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K281" t="inlineStr"/>
@@ -17660,13 +17660,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>49640.9</v>
+        <v>109632.69</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>599-58-CM26</t>
+          <t>1305552-66-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17686,17 +17686,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>ANDESTIC SPA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.031.392-0</t>
         </is>
       </c>
       <c r="K282" t="inlineStr"/>
@@ -17721,7 +17721,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>108751.26</v>
+        <v>50043.25</v>
       </c>
     </row>
     <row r="283">
@@ -17782,7 +17782,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>28955.72</v>
+        <v>29271.92</v>
       </c>
     </row>
     <row r="284">
@@ -17843,7 +17843,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>18921.53</v>
+        <v>19128.15</v>
       </c>
     </row>
     <row r="285">
@@ -17904,7 +17904,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>28206.67</v>
+        <v>28514.69</v>
       </c>
     </row>
     <row r="286">
@@ -17965,7 +17965,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>21821.7</v>
+        <v>22060</v>
       </c>
     </row>
     <row r="287">
@@ -18026,7 +18026,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>15102.79</v>
+        <v>15267.72</v>
       </c>
     </row>
     <row r="288">
@@ -18087,13 +18087,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>431231.97</v>
+        <v>435941.1</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1068243-2-CM26</t>
+          <t>4127-182-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18113,17 +18113,17 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>61.979.830-9</t>
+          <t>61.975.700-9</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ENERGIA</t>
+          <t>SUBSECRETARIA DE REDES ASISTENCIALES</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18133,12 +18133,12 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>APHIX INFORMATICA LIMITADA</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>76.170.582-2</t>
         </is>
       </c>
       <c r="K289" t="inlineStr"/>
@@ -18148,13 +18148,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>17278.59</v>
+        <v>8830.73</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>4127-182-CM26</t>
+          <t>1068243-2-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18174,17 +18174,17 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>61.975.700-9</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE REDES ASISTENCIALES</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18194,12 +18194,12 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>APHIX INFORMATICA LIMITADA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>76.170.582-2</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K290" t="inlineStr"/>
@@ -18209,13 +18209,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>8753.950000000001</v>
+        <v>17430.13</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>606-200-CM26</t>
+          <t>2735-84-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18240,12 +18240,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>60.513.000-3</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18255,12 +18255,12 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>ABISKO GROUP SPA</t>
+          <t>LUUK SPA</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>76.456.131-7</t>
+          <t>77.363.384-3</t>
         </is>
       </c>
       <c r="K291" t="inlineStr"/>
@@ -18270,7 +18270,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>22871.66</v>
+        <v>64113.26</v>
       </c>
     </row>
     <row r="292">
@@ -18331,13 +18331,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>38582.72</v>
+        <v>39136.74</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2735-84-CM26</t>
+          <t>606-200-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18362,12 +18362,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>60.513.000-3</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18377,12 +18377,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>LUUK SPA</t>
+          <t>ABISKO GROUP SPA</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>77.363.384-3</t>
+          <t>76.456.131-7</t>
         </is>
       </c>
       <c r="K293" t="inlineStr"/>
@@ -18392,7 +18392,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>63205.66</v>
+        <v>23200.08</v>
       </c>
     </row>
     <row r="294">
@@ -18453,7 +18453,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>39487.71</v>
+        <v>39805.72</v>
       </c>
     </row>
     <row r="295">
@@ -18514,7 +18514,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>16450.21</v>
+        <v>16576.62</v>
       </c>
     </row>
     <row r="296">
@@ -18575,7 +18575,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>32459.78</v>
+        <v>32199.67</v>
       </c>
     </row>
     <row r="297">
@@ -18636,7 +18636,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>31893.26</v>
+        <v>31442.28</v>
       </c>
     </row>
     <row r="298">
@@ -18697,13 +18697,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>29005.66</v>
+        <v>28831.2</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>45-113-CM26</t>
+          <t>758004-76-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -18728,12 +18728,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>Universidad de Chile</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18743,12 +18743,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>ZERVIZ</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.755.489-3</t>
         </is>
       </c>
       <c r="K299" t="inlineStr"/>
@@ -18758,13 +18758,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>53021.86</v>
+        <v>12167.84</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>758004-76-CM26</t>
+          <t>45-113-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -18789,12 +18789,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -18804,12 +18804,12 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>ZERVIZ</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>76.755.489-3</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K300" t="inlineStr"/>
@@ -18819,13 +18819,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>11983.89</v>
+        <v>53835.73</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2083-2-CM26</t>
+          <t>45-109-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -18850,12 +18850,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>71.294.800-0</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>CENTRO DE INFORMACION DE RECURSOS NATURALES</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -18865,12 +18865,12 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>Asimov Consultores SpA</t>
+          <t>DATCO CHILE S A</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>96.897.630-3</t>
         </is>
       </c>
       <c r="K301" t="inlineStr"/>
@@ -18880,13 +18880,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>31303.04</v>
+        <v>42282.45</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>621923-26-CM26</t>
+          <t>1075952-23-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -18906,17 +18906,17 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>53.314.945-6</t>
+          <t>62.000.580-0</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Superintendencia de Educación Superior</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -18926,12 +18926,12 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>77.077.350-4</t>
         </is>
       </c>
       <c r="K302" t="inlineStr"/>
@@ -18941,13 +18941,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>89270.78</v>
+        <v>15616.46</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>45-109-CM26</t>
+          <t>621923-26-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -18967,17 +18967,17 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>53.314.945-6</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -18987,12 +18987,12 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>DATCO CHILE S A</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>96.897.630-3</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K303" t="inlineStr"/>
@@ -19002,13 +19002,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>41472.06</v>
+        <v>91015.17999999999</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1075952-23-CM26</t>
+          <t>2083-2-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -19033,12 +19033,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>62.000.580-0</t>
+          <t>71.294.800-0</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Superintendencia de Educación Superior</t>
+          <t>CENTRO DE INFORMACION DE RECURSOS NATURALES</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19048,12 +19048,12 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>Asimov Consultores SpA</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K304" t="inlineStr"/>
@@ -19063,7 +19063,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>15317.16</v>
+        <v>31914.72</v>
       </c>
     </row>
     <row r="305">
@@ -19124,7 +19124,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>16664.23</v>
+        <v>17050.03</v>
       </c>
     </row>
     <row r="306">
@@ -19185,7 +19185,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>68123.78</v>
+        <v>69700.96000000001</v>
       </c>
     </row>
     <row r="307">
@@ -19246,7 +19246,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>32732.55</v>
+        <v>32980.05</v>
       </c>
     </row>
     <row r="308">
@@ -19307,7 +19307,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>37572.8</v>
+        <v>37721.09</v>
       </c>
     </row>
     <row r="309">
@@ -19368,13 +19368,13 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>39261.46</v>
+        <v>39416.42</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>538598-2171-CM26</t>
+          <t>2268-97-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19399,12 +19399,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>61.979.450-8</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>HOSPITAL METROPOLITANO DE SANTIAGO</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19414,12 +19414,12 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>77.842.230-1</t>
         </is>
       </c>
       <c r="K310" t="inlineStr"/>
@@ -19429,13 +19429,13 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>417776.85</v>
+        <v>83990.07000000001</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2268-97-CM26</t>
+          <t>538598-2171-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -19460,12 +19460,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>61.979.450-8</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>HOSPITAL METROPOLITANO DE SANTIAGO</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -19475,12 +19475,12 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>77.842.230-1</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K311" t="inlineStr"/>
@@ -19490,7 +19490,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>85040.11</v>
+        <v>412618.31</v>
       </c>
     </row>
     <row r="312">
@@ -19551,7 +19551,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>133615.09</v>
+        <v>131137.6</v>
       </c>
     </row>
     <row r="313">
@@ -19612,13 +19612,13 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>29325.73</v>
+        <v>28923.58</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2767-36-CM26</t>
+          <t>568963-123-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -19643,12 +19643,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>61.979.610-1</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>COMISION DEL SISTEMA NACIONAL DE CERTIFICACION DE COMPETENCIAS LABORALES</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -19658,12 +19658,12 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>KLEINROCK SPA</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>77.146.212-K</t>
         </is>
       </c>
       <c r="K314" t="inlineStr"/>
@@ -19673,13 +19673,13 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>32092.15</v>
+        <v>80565.07000000001</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>568963-123-CM26</t>
+          <t>2767-36-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -19704,12 +19704,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>61.979.610-1</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>COMISION DEL SISTEMA NACIONAL DE CERTIFICACION DE COMPETENCIAS LABORALES</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -19719,12 +19719,12 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>KLEINROCK SPA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>77.146.212-K</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K315" t="inlineStr"/>
@@ -19734,7 +19734,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>79843.36</v>
+        <v>32382.23</v>
       </c>
     </row>
     <row r="316">
@@ -19795,7 +19795,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>1690339.34</v>
+        <v>1696277.88</v>
       </c>
     </row>
     <row r="317">
@@ -19856,7 +19856,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>29627.47</v>
+        <v>29915.81</v>
       </c>
     </row>
     <row r="318">
@@ -19917,7 +19917,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>22031.5</v>
+        <v>22245.91</v>
       </c>
     </row>
     <row r="319">
@@ -19978,13 +19978,13 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>15803.64</v>
+        <v>15959.94</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1602-67-CM26</t>
+          <t>1602-68-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -20039,13 +20039,13 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>36324.34</v>
+        <v>24602.81</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>1602-68-CM26</t>
+          <t>1602-67-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -20100,7 +20100,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>24479.45</v>
+        <v>36507.4</v>
       </c>
     </row>
     <row r="322">
@@ -20161,7 +20161,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>76240.75</v>
+        <v>76538.36</v>
       </c>
     </row>
     <row r="323">
@@ -20222,7 +20222,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>17021.55</v>
+        <v>16936.63</v>
       </c>
     </row>
     <row r="324">
@@ -20283,13 +20283,13 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>26703</v>
+        <v>26569.78</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>730566-155-CM26</t>
+          <t>812261-62-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -20314,12 +20314,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -20329,12 +20329,12 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>77.754.348-2</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K325" t="inlineStr"/>
@@ -20344,13 +20344,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>54890.11</v>
+        <v>482098.69</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>812261-62-CM26</t>
+          <t>730566-155-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -20375,12 +20375,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -20390,12 +20390,12 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>77.754.348-2</t>
         </is>
       </c>
       <c r="K326" t="inlineStr"/>
@@ -20405,7 +20405,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>481036.15</v>
+        <v>55011.36</v>
       </c>
     </row>
     <row r="327">
@@ -20466,7 +20466,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>8939.08</v>
+        <v>8998.049999999999</v>
       </c>
     </row>
     <row r="328">
@@ -20527,7 +20527,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>18359.58</v>
+        <v>18480.71</v>
       </c>
     </row>
     <row r="329">
@@ -20588,7 +20588,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>37434.5</v>
+        <v>37523.24</v>
       </c>
     </row>
     <row r="330">
@@ -20649,7 +20649,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>38324.81</v>
+        <v>38415.67</v>
       </c>
     </row>
     <row r="331">
@@ -20710,7 +20710,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>52468.49</v>
+        <v>52823.77</v>
       </c>
     </row>
     <row r="332">
@@ -20771,7 +20771,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>30383.47</v>
+        <v>30598.47</v>
       </c>
     </row>
     <row r="333">
@@ -20832,7 +20832,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>15862.68</v>
+        <v>15813.8</v>
       </c>
     </row>
     <row r="334">
@@ -20893,13 +20893,13 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>37342.12</v>
+        <v>37227.05</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>757-389-CM26</t>
+          <t>1111089-207-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -20924,12 +20924,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>61.601.000-k</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -20939,12 +20939,12 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>METASOFT SOCIEDAD POR ACCIONES</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>76.213.064-5</t>
         </is>
       </c>
       <c r="K335" t="inlineStr"/>
@@ -20954,13 +20954,13 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>14031.21</v>
+        <v>41954.37</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1111089-207-CM26</t>
+          <t>757-389-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -20985,12 +20985,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>61.601.000-k</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -21000,12 +21000,12 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>METASOFT SOCIEDAD POR ACCIONES</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>76.213.064-5</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K336" t="inlineStr"/>
@@ -21015,7 +21015,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>42042.6</v>
+        <v>14001.76</v>
       </c>
     </row>
     <row r="337">
@@ -21076,7 +21076,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>914845.87</v>
+        <v>913082.5600000001</v>
       </c>
     </row>
     <row r="338">
@@ -21137,7 +21137,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>8159.82</v>
+        <v>8144.09</v>
       </c>
     </row>
     <row r="339">
@@ -21198,7 +21198,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>32529.1</v>
+        <v>32466.41</v>
       </c>
     </row>
     <row r="340">
@@ -21259,7 +21259,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>7262.24</v>
+        <v>7248.24</v>
       </c>
     </row>
     <row r="341">
@@ -21320,7 +21320,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>48028.85</v>
+        <v>47936.28</v>
       </c>
     </row>
     <row r="342">
@@ -21381,7 +21381,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>8249.17</v>
+        <v>8202.049999999999</v>
       </c>
     </row>
     <row r="343">
@@ -21442,7 +21442,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>15788.59</v>
+        <v>15535.01</v>
       </c>
     </row>
     <row r="344">
@@ -21503,13 +21503,13 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>69753.46000000001</v>
+        <v>68633.12</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2702-358-CM26</t>
+          <t>1111089-188-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -21534,12 +21534,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -21549,12 +21549,12 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>SOCIEDAD DE PROFESIONALES ON DEMAND AND RECURRING IT SERVICES LIMITADA</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>77.173.545-2</t>
         </is>
       </c>
       <c r="K345" t="inlineStr"/>
@@ -21564,7 +21564,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>10103.26</v>
+        <v>97132.32000000001</v>
       </c>
     </row>
     <row r="346">
@@ -21625,13 +21625,13 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>46263.52</v>
+        <v>45525.27</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1111089-188-CM26</t>
+          <t>2702-358-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -21656,12 +21656,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -21671,12 +21671,12 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE PROFESIONALES ON DEMAND AND RECURRING IT SERVICES LIMITADA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>77.173.545-2</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K347" t="inlineStr"/>
@@ -21686,7 +21686,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>98707.45</v>
+        <v>9942.030000000001</v>
       </c>
     </row>
     <row r="348">
@@ -21747,7 +21747,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>79253.71000000001</v>
+        <v>78337.60000000001</v>
       </c>
     </row>
     <row r="349">
@@ -21808,13 +21808,13 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>50854.08</v>
+        <v>50266.24</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2455-107-CM26</t>
+          <t>1147293-198-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -21839,12 +21839,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>69.071.000-5</t>
+          <t>70.930.000-8</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
+          <t>Fundación para la Innovación Agraria</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -21854,12 +21854,12 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>NEWTENBERG PUBLICACIONES DIGITALES LIMITADA</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>77.543.180-6</t>
         </is>
       </c>
       <c r="K350" t="inlineStr"/>
@@ -21869,13 +21869,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>261926.13</v>
+        <v>17306.45</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>711841-231-SE26</t>
+          <t>4666-1-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -21900,12 +21900,12 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -21915,32 +21915,28 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>ALTAVOZ SOCIEDAD ANONIMA</t>
+          <t>USERCODE SPA</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>96.827.350-7</t>
-        </is>
-      </c>
-      <c r="K351" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.347.464-8</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr"/>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>10530.05</v>
+        <v>21436.03</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>869591-36-CM26</t>
+          <t>711841-243-SE26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -21965,12 +21961,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>60.808.000-7</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -21980,28 +21976,32 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>XMS Business Solutions S.A.</t>
+          <t>ANTICIPA S A</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>76.249.938-k</t>
-        </is>
-      </c>
-      <c r="K352" t="inlineStr"/>
+          <t>96.771.610-3</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>45879.04</v>
+        <v>17375.86</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>711841-243-SE26</t>
+          <t>869591-36-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -22026,12 +22026,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>60.808.000-7</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -22041,32 +22041,28 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>ANTICIPA S A</t>
+          <t>XMS Business Solutions S.A.</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>96.771.610-3</t>
-        </is>
-      </c>
-      <c r="K353" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.249.938-k</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr"/>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>17460.36</v>
+        <v>45656.99</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>4666-1-CM26</t>
+          <t>711841-231-SE26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -22091,12 +22087,12 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -22106,28 +22102,32 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>USERCODE SPA</t>
+          <t>ALTAVOZ SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>77.347.464-8</t>
-        </is>
-      </c>
-      <c r="K354" t="inlineStr"/>
+          <t>96.827.350-7</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>21540.28</v>
+        <v>10479.08</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1147293-198-CM26</t>
+          <t>2455-107-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -22152,12 +22152,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>70.930.000-8</t>
+          <t>69.071.000-5</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Fundación para la Innovación Agraria</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -22167,12 +22167,12 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>NEWTENBERG PUBLICACIONES DIGITALES LIMITADA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>77.543.180-6</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K355" t="inlineStr"/>
@@ -22182,13 +22182,13 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>17390.62</v>
+        <v>260658.45</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1549-3396-CM26</t>
+          <t>721703-316-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -22213,12 +22213,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.980.230-6</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>AGENCIA DE CALIDAD DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -22228,12 +22228,12 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>76.891.821-k</t>
         </is>
       </c>
       <c r="K356" t="inlineStr"/>
@@ -22243,13 +22243,13 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>12085.64</v>
+        <v>20126.92</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>721703-316-CM26</t>
+          <t>1549-3396-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -22274,12 +22274,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>61.980.230-6</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>AGENCIA DE CALIDAD DE LA EDUCACION</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -22289,12 +22289,12 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K357" t="inlineStr"/>
@@ -22304,7 +22304,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>19991.55</v>
+        <v>12167.48</v>
       </c>
     </row>
     <row r="358">
@@ -22365,7 +22365,373 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>134762.36</v>
+        <v>135674.88</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>1314-20-CM26</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>60.706.000-2</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>76.444.489-2</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr"/>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M359" s="2" t="n">
+        <v>16183.69</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2273-537-CM26</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>69.253.800-5</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA PINTANA</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>PAIS DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>77.015.597-5</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr"/>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M360" s="2" t="n">
+        <v>10717.53</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>4928-75-CM26</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>61.938.500-4</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>INFO WORLD SA</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>96.532.020-2</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr"/>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M361" s="2" t="n">
+        <v>38233.24</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>1314-13-CM26</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>60.706.000-2</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M362" s="2" t="n">
+        <v>32258.59</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>584105-190-CM26</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>61.979.830-9</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE ENERGIA</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>TCHILECOM</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>77.349.120-8</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr"/>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M363" s="2" t="n">
+        <v>33321.71</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>599-140-CM26</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>METASOFT SOCIEDAD POR ACCIONES</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>76.213.064-5</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr"/>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M364" s="2" t="n">
+        <v>37874.54</v>
       </c>
     </row>
   </sheetData>
